--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N40_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N40_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>33.22986072693659</v>
+        <v>5.399852368127196</v>
       </c>
       <c r="D2" t="n">
-        <v>34.0031162942157</v>
+        <v>5.525506397810052</v>
       </c>
       <c r="E2" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F2" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.70024184373262</v>
+        <v>6.776289299606551</v>
       </c>
       <c r="D3" t="n">
-        <v>41.56317302527624</v>
+        <v>6.754015616607388</v>
       </c>
       <c r="E3" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F3" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.40325948030479</v>
+        <v>7.540529665549529</v>
       </c>
       <c r="D4" t="n">
-        <v>46.61074126189066</v>
+        <v>7.574245455057232</v>
       </c>
       <c r="E4" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F4" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.90239738206954</v>
+        <v>2.259139574586301</v>
       </c>
       <c r="D5" t="n">
-        <v>12.89670841553189</v>
+        <v>2.095715117523932</v>
       </c>
       <c r="E5" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F5" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.30227431268109</v>
+        <v>5.249119575810677</v>
       </c>
       <c r="D6" t="n">
-        <v>37.51616983706549</v>
+        <v>6.096377598523143</v>
       </c>
       <c r="E6" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F6" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>41.97277265780088</v>
+        <v>6.820575556892644</v>
       </c>
       <c r="D7" t="n">
-        <v>41.90763653560052</v>
+        <v>6.809990937035085</v>
       </c>
       <c r="E7" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F7" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.82438317461282</v>
+        <v>4.033962265874584</v>
       </c>
       <c r="D8" t="n">
-        <v>31.4101579857752</v>
+        <v>5.104150672688471</v>
       </c>
       <c r="E8" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F8" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>37.27430882876845</v>
+        <v>6.057075184674874</v>
       </c>
       <c r="D9" t="n">
-        <v>37.98536735808074</v>
+        <v>6.172622195688121</v>
       </c>
       <c r="E9" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F9" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.89637854157921</v>
+        <v>2.908161513006621</v>
       </c>
       <c r="D10" t="n">
-        <v>8.54400374531753</v>
+        <v>1.388400608614099</v>
       </c>
       <c r="E10" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F10" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>23.12362030784129</v>
+        <v>3.75758830002421</v>
       </c>
       <c r="D11" t="n">
-        <v>29.70279825386464</v>
+        <v>4.826704716253004</v>
       </c>
       <c r="E11" t="n">
-        <v>10.40052667758087</v>
+        <v>1.690085585106891</v>
       </c>
       <c r="F11" t="n">
-        <v>11.80525806930112</v>
+        <v>1.918354436261432</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
